--- a/backend/uploads/KZLEAP_DATA_TABLE.xlsx
+++ b/backend/uploads/KZLEAP_DATA_TABLE.xlsx
@@ -1,63 +1,226 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10608"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/aliyaseitova/Downloads/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{744A95D4-0226-354F-8639-0293506953B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="17360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="historical_energy" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="historical_demo" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="elec_mix" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="scenarios" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ndc_targets" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="historical_energy" sheetId="1" r:id="rId1"/>
+    <sheet name="historical_demo" sheetId="2" r:id="rId2"/>
+    <sheet name="elec_mix" sheetId="3" r:id="rId3"/>
+    <sheet name="scenarios" sheetId="4" r:id="rId4"/>
+    <sheet name="ndc_targets" sheetId="5" r:id="rId5"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="48">
+  <si>
+    <t># TPES_Mtoe = Total Primary Energy Consumption (внутреннее потребление). Источник: ваши данные. Electricity: IRENA/countryeconomy.com. CO2: World Bank/IEA.</t>
+  </si>
+  <si>
+    <t>Year</t>
+  </si>
+  <si>
+    <t>TPES_Mtoe</t>
+  </si>
+  <si>
+    <t>Electricity_TWh</t>
+  </si>
+  <si>
+    <t>CO2_Mt</t>
+  </si>
+  <si>
+    <t># Source: World Bank WDI — Population, Urban %, GDP (current USD B). WorkingAge_pct estimated.</t>
+  </si>
+  <si>
+    <t>Population_M</t>
+  </si>
+  <si>
+    <t>WorkingAge_pct</t>
+  </si>
+  <si>
+    <t>Urban_pct</t>
+  </si>
+  <si>
+    <t>GDP_USD_B</t>
+  </si>
+  <si>
+    <t># Source: IRENA / countryeconomy.com. Base year 2023. Renewable share 12.4% of 113 TWh.</t>
+  </si>
+  <si>
+    <t>Source</t>
+  </si>
+  <si>
+    <t>Share_pct</t>
+  </si>
+  <si>
+    <t>coal</t>
+  </si>
+  <si>
+    <t>gas</t>
+  </si>
+  <si>
+    <t>hydro</t>
+  </si>
+  <si>
+    <t>wind</t>
+  </si>
+  <si>
+    <t>solar</t>
+  </si>
+  <si>
+    <t>nuclear</t>
+  </si>
+  <si>
+    <t># Scenario parameters. Adjust to your policy assumptions.</t>
+  </si>
+  <si>
+    <t>Parameter</t>
+  </si>
+  <si>
+    <t>BAU</t>
+  </si>
+  <si>
+    <t>MT</t>
+  </si>
+  <si>
+    <t>DD</t>
+  </si>
+  <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>Business as Usual</t>
+  </si>
+  <si>
+    <t>Moderate Transition</t>
+  </si>
+  <si>
+    <t>Deep Decarbonization</t>
+  </si>
+  <si>
+    <t>description</t>
+  </si>
+  <si>
+    <t>Current policy, no new measures</t>
+  </si>
+  <si>
+    <t>NDC targets met, gradual coal phase-down</t>
+  </si>
+  <si>
+    <t>Carbon neutrality 2060, rapid RE scale-up</t>
+  </si>
+  <si>
+    <t>gdp_growth</t>
+  </si>
+  <si>
+    <t>energy_intensity_change</t>
+  </si>
+  <si>
+    <t>coal_share_2050</t>
+  </si>
+  <si>
+    <t>renewables_2030</t>
+  </si>
+  <si>
+    <t>renewables_2050</t>
+  </si>
+  <si>
+    <t>nuclear_gw_2035</t>
+  </si>
+  <si>
+    <t>co2_price_2030</t>
+  </si>
+  <si>
+    <t>co2_price_2050</t>
+  </si>
+  <si>
+    <t>ev_share_2050</t>
+  </si>
+  <si>
+    <t># Kazakhstan NDC (updated 2023): -15% unconditional, -25% conditional vs 1990. Neutrality 2060.</t>
+  </si>
+  <si>
+    <t>Value</t>
+  </si>
+  <si>
+    <t>base_year</t>
+  </si>
+  <si>
+    <t>base_co2_mt</t>
+  </si>
+  <si>
+    <t>ndc_unconditional_pct</t>
+  </si>
+  <si>
+    <t>ndc_conditional_pct</t>
+  </si>
+  <si>
+    <t>neutrality_year</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <i val="1"/>
-      <color rgb="001D6B48"/>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF1D6B48"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="4">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E8F5E9"/>
+        <fgColor rgb="FFE8F5E9"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001D6B48"/>
+        <fgColor rgb="FF1D6B48"/>
       </patternFill>
     </fill>
   </fills>
@@ -71,110 +234,52 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00CCCCCC"/>
+        <color rgb="FFCCCCCC"/>
       </left>
       <right style="thin">
-        <color rgb="00CCCCCC"/>
+        <color rgb="FFCCCCCC"/>
       </right>
       <top style="thin">
-        <color rgb="00CCCCCC"/>
+        <color rgb="FFCCCCCC"/>
       </top>
       <bottom style="thin">
-        <color rgb="00CCCCCC"/>
+        <color rgb="FFCCCCCC"/>
       </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="6">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -462,538 +567,516 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D37"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col width="128" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="19" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
+    <col min="1" max="1" width="128" customWidth="1"/>
+    <col min="2" max="2" width="13" customWidth="1"/>
+    <col min="3" max="3" width="19" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t># TPES_Mtoe = Total Primary Energy Consumption (внутреннее потребление). Источник: ваши данные. Electricity: IRENA/countryeconomy.com. CO2: World Bank/IEA.</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Year</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>TPES_Mtoe</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>Electricity_TWh</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>CO2_Mt</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="n">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A3" s="3">
         <v>1990</v>
       </c>
-      <c r="B3" s="4" t="n">
-        <v>73.90000000000001</v>
-      </c>
-      <c r="C3" s="4" t="n">
-        <v>87.40000000000001</v>
-      </c>
-      <c r="D3" s="4" t="n">
+      <c r="B3" s="4">
+        <v>73.900000000000006</v>
+      </c>
+      <c r="C3" s="4">
+        <v>87.4</v>
+      </c>
+      <c r="D3" s="4">
         <v>248.6</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="3" t="n">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A4" s="3">
         <v>1991</v>
       </c>
-      <c r="B4" s="4" t="n">
-        <v>73.90000000000001</v>
-      </c>
-      <c r="C4" s="4" t="n">
+      <c r="B4" s="4">
+        <v>73.900000000000006</v>
+      </c>
+      <c r="C4" s="4">
         <v>83</v>
       </c>
-      <c r="D4" s="4" t="n">
-        <v>259.9</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="n">
+      <c r="D4" s="4">
+        <v>259.89999999999998</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A5" s="3">
         <v>1992</v>
       </c>
-      <c r="B5" s="4" t="n">
+      <c r="B5" s="4">
         <v>72.8</v>
       </c>
-      <c r="C5" s="4" t="n">
-        <v>78.59999999999999</v>
-      </c>
-      <c r="D5" s="4" t="n">
+      <c r="C5" s="4">
+        <v>78.599999999999994</v>
+      </c>
+      <c r="D5" s="4">
         <v>265.3</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="3" t="n">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A6" s="3">
         <v>1993</v>
       </c>
-      <c r="B6" s="4" t="n">
+      <c r="B6" s="4">
         <v>64.3</v>
       </c>
-      <c r="C6" s="4" t="n">
-        <v>73.59999999999999</v>
-      </c>
-      <c r="D6" s="4" t="n">
+      <c r="C6" s="4">
+        <v>73.599999999999994</v>
+      </c>
+      <c r="D6" s="4">
         <v>226.1</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="3" t="n">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A7" s="3">
         <v>1994</v>
       </c>
-      <c r="B7" s="4" t="n">
+      <c r="B7" s="4">
         <v>57.3</v>
       </c>
-      <c r="C7" s="4" t="n">
+      <c r="C7" s="4">
         <v>63.2</v>
       </c>
-      <c r="D7" s="4" t="n">
+      <c r="D7" s="4">
         <v>203.8</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="3" t="n">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A8" s="3">
         <v>1995</v>
       </c>
-      <c r="B8" s="4" t="n">
+      <c r="B8" s="4">
         <v>51.5</v>
       </c>
-      <c r="C8" s="4" t="n">
+      <c r="C8" s="4">
         <v>63.2</v>
       </c>
-      <c r="D8" s="4" t="n">
+      <c r="D8" s="4">
         <v>180.3</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="3" t="n">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A9" s="3">
         <v>1996</v>
       </c>
-      <c r="B9" s="4" t="n">
+      <c r="B9" s="4">
         <v>44.8</v>
       </c>
-      <c r="C9" s="4" t="n">
+      <c r="C9" s="4">
         <v>56</v>
       </c>
-      <c r="D9" s="4" t="n">
+      <c r="D9" s="4">
         <v>158</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="3" t="n">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A10" s="3">
         <v>1997</v>
       </c>
-      <c r="B10" s="4" t="n">
+      <c r="B10" s="4">
         <v>39.6</v>
       </c>
-      <c r="C10" s="4" t="n">
+      <c r="C10" s="4">
         <v>49.5</v>
       </c>
-      <c r="D10" s="4" t="n">
-        <v>137.3</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="n">
+      <c r="D10" s="4">
+        <v>137.30000000000001</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A11" s="3">
         <v>1998</v>
       </c>
-      <c r="B11" s="4" t="n">
-        <v>37.2</v>
-      </c>
-      <c r="C11" s="4" t="n">
+      <c r="B11" s="4">
+        <v>37.200000000000003</v>
+      </c>
+      <c r="C11" s="4">
         <v>46.6</v>
       </c>
-      <c r="D11" s="4" t="n">
+      <c r="D11" s="4">
         <v>141.6</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="3" t="n">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A12" s="3">
         <v>1999</v>
       </c>
-      <c r="B12" s="4" t="n">
+      <c r="B12" s="4">
         <v>35</v>
       </c>
-      <c r="C12" s="4" t="n">
+      <c r="C12" s="4">
         <v>45</v>
       </c>
-      <c r="D12" s="4" t="n">
+      <c r="D12" s="4">
         <v>129.6</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="3" t="n">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A13" s="3">
         <v>2000</v>
       </c>
-      <c r="B13" s="4" t="n">
+      <c r="B13" s="4">
         <v>31.8</v>
       </c>
-      <c r="C13" s="4" t="n">
+      <c r="C13" s="4">
         <v>48.6</v>
       </c>
-      <c r="D13" s="4" t="n">
-        <v>132.2</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="n">
+      <c r="D13" s="4">
+        <v>132.19999999999999</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A14" s="3">
         <v>2001</v>
       </c>
-      <c r="B14" s="4" t="n">
-        <v>35.8</v>
-      </c>
-      <c r="C14" s="4" t="n">
+      <c r="B14" s="4">
+        <v>35.799999999999997</v>
+      </c>
+      <c r="C14" s="4">
         <v>53.8</v>
       </c>
-      <c r="D14" s="4" t="n">
+      <c r="D14" s="4">
         <v>130.5</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="3" t="n">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A15" s="3">
         <v>2002</v>
       </c>
-      <c r="B15" s="4" t="n">
+      <c r="B15" s="4">
         <v>36.5</v>
       </c>
-      <c r="C15" s="4" t="n">
+      <c r="C15" s="4">
         <v>55.3</v>
       </c>
-      <c r="D15" s="4" t="n">
+      <c r="D15" s="4">
         <v>145.5</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="3" t="n">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A16" s="3">
         <v>2003</v>
       </c>
-      <c r="B16" s="4" t="n">
+      <c r="B16" s="4">
         <v>40</v>
       </c>
-      <c r="C16" s="4" t="n">
+      <c r="C16" s="4">
         <v>60.5</v>
       </c>
-      <c r="D16" s="4" t="n">
+      <c r="D16" s="4">
         <v>162.1</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="3" t="n">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A17" s="3">
         <v>2004</v>
       </c>
-      <c r="B17" s="4" t="n">
+      <c r="B17" s="4">
         <v>42.2</v>
       </c>
-      <c r="C17" s="4" t="n">
+      <c r="C17" s="4">
         <v>63.3</v>
       </c>
-      <c r="D17" s="4" t="n">
+      <c r="D17" s="4">
         <v>174.6</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="3" t="n">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A18" s="3">
         <v>2005</v>
       </c>
-      <c r="B18" s="4" t="n">
+      <c r="B18" s="4">
         <v>43.4</v>
       </c>
-      <c r="C18" s="4" t="n">
+      <c r="C18" s="4">
         <v>64.2</v>
       </c>
-      <c r="D18" s="4" t="n">
+      <c r="D18" s="4">
         <v>187.6</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="3" t="n">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A19" s="3">
         <v>2006</v>
       </c>
-      <c r="B19" s="4" t="n">
+      <c r="B19" s="4">
         <v>46.7</v>
       </c>
-      <c r="C19" s="4" t="n">
+      <c r="C19" s="4">
         <v>67.7</v>
       </c>
-      <c r="D19" s="4" t="n">
+      <c r="D19" s="4">
         <v>210.2</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="3" t="n">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A20" s="3">
         <v>2007</v>
       </c>
-      <c r="B20" s="4" t="n">
+      <c r="B20" s="4">
         <v>51.8</v>
       </c>
-      <c r="C20" s="4" t="n">
-        <v>72.40000000000001</v>
-      </c>
-      <c r="D20" s="4" t="n">
+      <c r="C20" s="4">
+        <v>72.400000000000006</v>
+      </c>
+      <c r="D20" s="4">
         <v>219.6</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="3" t="n">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A21" s="3">
         <v>2008</v>
       </c>
-      <c r="B21" s="4" t="n">
+      <c r="B21" s="4">
         <v>54.6</v>
       </c>
-      <c r="C21" s="4" t="n">
-        <v>75.90000000000001</v>
-      </c>
-      <c r="D21" s="4" t="n">
-        <v>259.6</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="3" t="n">
+      <c r="C21" s="4">
+        <v>75.900000000000006</v>
+      </c>
+      <c r="D21" s="4">
+        <v>259.60000000000002</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A22" s="3">
         <v>2009</v>
       </c>
-      <c r="B22" s="4" t="n">
+      <c r="B22" s="4">
         <v>48.9</v>
       </c>
-      <c r="C22" s="4" t="n">
+      <c r="C22" s="4">
         <v>74.3</v>
       </c>
-      <c r="D22" s="4" t="n">
+      <c r="D22" s="4">
         <v>231.4</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="3" t="n">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A23" s="3">
         <v>2010</v>
       </c>
-      <c r="B23" s="4" t="n">
+      <c r="B23" s="4">
         <v>52.5</v>
       </c>
-      <c r="C23" s="4" t="n">
-        <v>78.09999999999999</v>
-      </c>
-      <c r="D23" s="4" t="n">
+      <c r="C23" s="4">
+        <v>78.099999999999994</v>
+      </c>
+      <c r="D23" s="4">
         <v>249.9</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="3" t="n">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A24" s="3">
         <v>2011</v>
       </c>
-      <c r="B24" s="4" t="n">
+      <c r="B24" s="4">
         <v>59.7</v>
       </c>
-      <c r="C24" s="4" t="n">
+      <c r="C24" s="4">
         <v>81.8</v>
       </c>
-      <c r="D24" s="4" t="n">
+      <c r="D24" s="4">
         <v>268.3</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="3" t="n">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A25" s="3">
         <v>2012</v>
       </c>
-      <c r="B25" s="4" t="n">
+      <c r="B25" s="4">
         <v>62.8</v>
       </c>
-      <c r="C25" s="4" t="n">
-        <v>87.59999999999999</v>
-      </c>
-      <c r="D25" s="4" t="n">
+      <c r="C25" s="4">
+        <v>87.6</v>
+      </c>
+      <c r="D25" s="4">
         <v>267.3</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="3" t="n">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A26" s="3">
         <v>2013</v>
       </c>
-      <c r="B26" s="4" t="n">
+      <c r="B26" s="4">
         <v>62.9</v>
       </c>
-      <c r="C26" s="4" t="n">
+      <c r="C26" s="4">
         <v>97.3</v>
       </c>
-      <c r="D26" s="4" t="n">
+      <c r="D26" s="4">
         <v>286.2</v>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="3" t="n">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A27" s="3">
         <v>2014</v>
       </c>
-      <c r="B27" s="4" t="n">
-        <v>66.09999999999999</v>
-      </c>
-      <c r="C27" s="4" t="n">
+      <c r="B27" s="4">
+        <v>66.099999999999994</v>
+      </c>
+      <c r="C27" s="4">
         <v>90</v>
       </c>
-      <c r="D27" s="4" t="n">
+      <c r="D27" s="4">
         <v>232.3</v>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="3" t="n">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A28" s="3">
         <v>2015</v>
       </c>
-      <c r="B28" s="4" t="n">
+      <c r="B28" s="4">
         <v>54.7</v>
       </c>
-      <c r="C28" s="4" t="n">
+      <c r="C28" s="4">
         <v>91.8</v>
       </c>
-      <c r="D28" s="4" t="n">
+      <c r="D28" s="4">
         <v>205.4</v>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="3" t="n">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A29" s="3">
         <v>2016</v>
       </c>
-      <c r="B29" s="4" t="n">
+      <c r="B29" s="4">
         <v>61.1</v>
       </c>
-      <c r="C29" s="4" t="n">
-        <v>94.59999999999999</v>
-      </c>
-      <c r="D29" s="4" t="n">
+      <c r="C29" s="4">
+        <v>94.6</v>
+      </c>
+      <c r="D29" s="4">
         <v>215.7</v>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="3" t="n">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A30" s="3">
         <v>2017</v>
       </c>
-      <c r="B30" s="4" t="n">
+      <c r="B30" s="4">
         <v>65.8</v>
       </c>
-      <c r="C30" s="4" t="n">
+      <c r="C30" s="4">
         <v>103.1</v>
       </c>
-      <c r="D30" s="4" t="n">
+      <c r="D30" s="4">
         <v>227.7</v>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="3" t="n">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A31" s="3">
         <v>2018</v>
       </c>
-      <c r="B31" s="4" t="n">
+      <c r="B31" s="4">
         <v>67.8</v>
       </c>
-      <c r="C31" s="4" t="n">
+      <c r="C31" s="4">
         <v>107.6</v>
       </c>
-      <c r="D31" s="4" t="n">
+      <c r="D31" s="4">
         <v>228.9</v>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="3" t="n">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A32" s="3">
         <v>2019</v>
       </c>
-      <c r="B32" s="4" t="n">
+      <c r="B32" s="4">
         <v>68.7</v>
       </c>
-      <c r="C32" s="4" t="n">
+      <c r="C32" s="4">
         <v>106.9</v>
       </c>
-      <c r="D32" s="4" t="n">
+      <c r="D32" s="4">
         <v>216.9</v>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="3" t="n">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A33" s="3">
         <v>2020</v>
       </c>
-      <c r="B33" s="4" t="n">
+      <c r="B33" s="4">
         <v>63.3</v>
       </c>
-      <c r="C33" s="4" t="n">
+      <c r="C33" s="4">
         <v>110.9</v>
       </c>
-      <c r="D33" s="4" t="n">
+      <c r="D33" s="4">
         <v>224.7</v>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="3" t="n">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A34" s="3">
         <v>2021</v>
       </c>
-      <c r="B34" s="4" t="n">
+      <c r="B34" s="4">
         <v>70.7</v>
       </c>
-      <c r="C34" s="4" t="n">
+      <c r="C34" s="4">
         <v>115.1</v>
       </c>
-      <c r="D34" s="4" t="n">
+      <c r="D34" s="4">
         <v>244.9</v>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="3" t="n">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A35" s="3">
         <v>2022</v>
       </c>
-      <c r="B35" s="4" t="n">
-        <v>70.40000000000001</v>
-      </c>
-      <c r="C35" s="4" t="n">
+      <c r="B35" s="4">
+        <v>70.400000000000006</v>
+      </c>
+      <c r="C35" s="4">
         <v>113.6</v>
       </c>
-      <c r="D35" s="4" t="n">
+      <c r="D35" s="4">
         <v>240.2</v>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="3" t="n">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A36" s="3">
         <v>2023</v>
       </c>
-      <c r="B36" s="4" t="n">
+      <c r="B36" s="4">
         <v>72.7</v>
       </c>
-      <c r="C36" s="4" t="n">
+      <c r="C36" s="4">
         <v>113.2</v>
       </c>
-      <c r="D36" s="4" t="n">
-        <v>239.9</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="3" t="n">
-        <v>2024</v>
-      </c>
-      <c r="B37" s="4" t="n">
-        <v>74.09999999999999</v>
-      </c>
-      <c r="C37" s="4" t="n">
-        <v>122.8</v>
-      </c>
-      <c r="D37" s="4" t="n">
-        <v>228</v>
-      </c>
+      <c r="D36" s="4">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A37" s="3"/>
+      <c r="B37" s="4"/>
+      <c r="C37" s="4"/>
+      <c r="D37" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1001,629 +1084,612 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:E37"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col width="98" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
+    <col min="1" max="1" width="98" customWidth="1"/>
+    <col min="2" max="2" width="16" customWidth="1"/>
+    <col min="3" max="3" width="18" customWidth="1"/>
+    <col min="4" max="5" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t># Source: World Bank WDI — Population, Urban %, GDP (current USD B). WorkingAge_pct estimated.</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Year</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>Population_M</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>WorkingAge_pct</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>Urban_pct</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>GDP_USD_B</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="n">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A3" s="3">
         <v>1990</v>
       </c>
-      <c r="B3" s="4" t="n">
+      <c r="B3" s="4">
         <v>16.5</v>
       </c>
-      <c r="C3" s="4" t="n">
+      <c r="C3" s="4">
         <v>61</v>
       </c>
-      <c r="D3" s="4" t="n">
+      <c r="D3" s="4">
         <v>57</v>
       </c>
-      <c r="E3" s="4" t="n">
+      <c r="E3" s="4">
         <v>26.9</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="3" t="n">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A4" s="3">
         <v>1991</v>
       </c>
-      <c r="B4" s="4" t="n">
-        <v>16.6</v>
-      </c>
-      <c r="C4" s="4" t="n">
+      <c r="B4" s="4">
+        <v>16.600000000000001</v>
+      </c>
+      <c r="C4" s="4">
         <v>61.5</v>
       </c>
-      <c r="D4" s="4" t="n">
+      <c r="D4" s="4">
         <v>57</v>
       </c>
-      <c r="E4" s="5" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="n">
+      <c r="E4" s="5"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A5" s="3">
         <v>1992</v>
       </c>
-      <c r="B5" s="4" t="n">
+      <c r="B5" s="4">
         <v>16.5</v>
       </c>
-      <c r="C5" s="4" t="n">
+      <c r="C5" s="4">
         <v>62</v>
       </c>
-      <c r="D5" s="4" t="n">
+      <c r="D5" s="4">
         <v>57</v>
       </c>
-      <c r="E5" s="5" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="n">
+      <c r="E5" s="5"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A6" s="3">
         <v>1993</v>
       </c>
-      <c r="B6" s="4" t="n">
-        <v>16.4</v>
-      </c>
-      <c r="C6" s="4" t="n">
+      <c r="B6" s="4">
+        <v>16.399999999999999</v>
+      </c>
+      <c r="C6" s="4">
         <v>62.5</v>
       </c>
-      <c r="D6" s="4" t="n">
+      <c r="D6" s="4">
         <v>57</v>
       </c>
-      <c r="E6" s="5" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="n">
+      <c r="E6" s="5"/>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A7" s="3">
         <v>1994</v>
       </c>
-      <c r="B7" s="4" t="n">
-        <v>16.1</v>
-      </c>
-      <c r="C7" s="4" t="n">
+      <c r="B7" s="4">
+        <v>16.100000000000001</v>
+      </c>
+      <c r="C7" s="4">
         <v>63</v>
       </c>
-      <c r="D7" s="4" t="n">
+      <c r="D7" s="4">
         <v>56.5</v>
       </c>
-      <c r="E7" s="5" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="n">
+      <c r="E7" s="5"/>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A8" s="3">
         <v>1995</v>
       </c>
-      <c r="B8" s="4" t="n">
+      <c r="B8" s="4">
         <v>15.8</v>
       </c>
-      <c r="C8" s="4" t="n">
+      <c r="C8" s="4">
         <v>63.5</v>
       </c>
-      <c r="D8" s="4" t="n">
+      <c r="D8" s="4">
         <v>56</v>
       </c>
-      <c r="E8" s="5" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="n">
+      <c r="E8" s="5"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A9" s="3">
         <v>1996</v>
       </c>
-      <c r="B9" s="4" t="n">
+      <c r="B9" s="4">
         <v>15.6</v>
       </c>
-      <c r="C9" s="4" t="n">
+      <c r="C9" s="4">
         <v>64</v>
       </c>
-      <c r="D9" s="4" t="n">
+      <c r="D9" s="4">
         <v>55.5</v>
       </c>
-      <c r="E9" s="5" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="n">
+      <c r="E9" s="5"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A10" s="3">
         <v>1997</v>
       </c>
-      <c r="B10" s="4" t="n">
+      <c r="B10" s="4">
         <v>15.4</v>
       </c>
-      <c r="C10" s="4" t="n">
+      <c r="C10" s="4">
         <v>64</v>
       </c>
-      <c r="D10" s="4" t="n">
+      <c r="D10" s="4">
         <v>55</v>
       </c>
-      <c r="E10" s="5" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="n">
+      <c r="E10" s="5"/>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A11" s="3">
         <v>1998</v>
       </c>
-      <c r="B11" s="4" t="n">
+      <c r="B11" s="4">
         <v>15.1</v>
       </c>
-      <c r="C11" s="4" t="n">
+      <c r="C11" s="4">
         <v>63.5</v>
       </c>
-      <c r="D11" s="4" t="n">
+      <c r="D11" s="4">
         <v>55</v>
       </c>
-      <c r="E11" s="5" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="n">
+      <c r="E11" s="5"/>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A12" s="3">
         <v>1999</v>
       </c>
-      <c r="B12" s="4" t="n">
+      <c r="B12" s="4">
         <v>14.9</v>
       </c>
-      <c r="C12" s="4" t="n">
+      <c r="C12" s="4">
         <v>63</v>
       </c>
-      <c r="D12" s="4" t="n">
+      <c r="D12" s="4">
         <v>55</v>
       </c>
-      <c r="E12" s="5" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="n">
+      <c r="E12" s="5"/>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A13" s="3">
         <v>2000</v>
       </c>
-      <c r="B13" s="4" t="n">
+      <c r="B13" s="4">
         <v>14.9</v>
       </c>
-      <c r="C13" s="4" t="n">
+      <c r="C13" s="4">
         <v>63.5</v>
       </c>
-      <c r="D13" s="4" t="n">
+      <c r="D13" s="4">
         <v>55</v>
       </c>
-      <c r="E13" s="4" t="n">
+      <c r="E13" s="4">
         <v>18.3</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="3" t="n">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A14" s="3">
         <v>2001</v>
       </c>
-      <c r="B14" s="4" t="n">
+      <c r="B14" s="4">
         <v>14.9</v>
       </c>
-      <c r="C14" s="4" t="n">
+      <c r="C14" s="4">
         <v>64</v>
       </c>
-      <c r="D14" s="4" t="n">
+      <c r="D14" s="4">
         <v>54.5</v>
       </c>
-      <c r="E14" s="4" t="n">
+      <c r="E14" s="4">
         <v>22.2</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="3" t="n">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A15" s="3">
         <v>2002</v>
       </c>
-      <c r="B15" s="4" t="n">
+      <c r="B15" s="4">
         <v>14.9</v>
       </c>
-      <c r="C15" s="4" t="n">
+      <c r="C15" s="4">
         <v>64.5</v>
       </c>
-      <c r="D15" s="4" t="n">
+      <c r="D15" s="4">
         <v>54</v>
       </c>
-      <c r="E15" s="4" t="n">
+      <c r="E15" s="4">
         <v>24.6</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="3" t="n">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A16" s="3">
         <v>2003</v>
       </c>
-      <c r="B16" s="4" t="n">
+      <c r="B16" s="4">
         <v>15</v>
       </c>
-      <c r="C16" s="4" t="n">
+      <c r="C16" s="4">
         <v>65</v>
       </c>
-      <c r="D16" s="4" t="n">
+      <c r="D16" s="4">
         <v>53.5</v>
       </c>
-      <c r="E16" s="4" t="n">
+      <c r="E16" s="4">
         <v>30.8</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="3" t="n">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A17" s="3">
         <v>2004</v>
       </c>
-      <c r="B17" s="4" t="n">
+      <c r="B17" s="4">
         <v>15.1</v>
       </c>
-      <c r="C17" s="4" t="n">
+      <c r="C17" s="4">
         <v>65.5</v>
       </c>
-      <c r="D17" s="4" t="n">
+      <c r="D17" s="4">
         <v>53.5</v>
       </c>
-      <c r="E17" s="4" t="n">
+      <c r="E17" s="4">
         <v>43.2</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="3" t="n">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A18" s="3">
         <v>2005</v>
       </c>
-      <c r="B18" s="4" t="n">
+      <c r="B18" s="4">
         <v>15.2</v>
       </c>
-      <c r="C18" s="4" t="n">
+      <c r="C18" s="4">
         <v>66</v>
       </c>
-      <c r="D18" s="4" t="n">
+      <c r="D18" s="4">
         <v>53.5</v>
       </c>
-      <c r="E18" s="4" t="n">
+      <c r="E18" s="4">
         <v>57.1</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="3" t="n">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A19" s="3">
         <v>2006</v>
       </c>
-      <c r="B19" s="4" t="n">
+      <c r="B19" s="4">
         <v>15.4</v>
       </c>
-      <c r="C19" s="4" t="n">
+      <c r="C19" s="4">
         <v>66.5</v>
       </c>
-      <c r="D19" s="4" t="n">
+      <c r="D19" s="4">
         <v>53.5</v>
       </c>
-      <c r="E19" s="4" t="n">
+      <c r="E19" s="4">
         <v>81</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="3" t="n">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A20" s="3">
         <v>2007</v>
       </c>
-      <c r="B20" s="4" t="n">
+      <c r="B20" s="4">
         <v>15.6</v>
       </c>
-      <c r="C20" s="4" t="n">
+      <c r="C20" s="4">
         <v>67</v>
       </c>
-      <c r="D20" s="4" t="n">
+      <c r="D20" s="4">
         <v>53.5</v>
       </c>
-      <c r="E20" s="4" t="n">
+      <c r="E20" s="4">
         <v>104.9</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="3" t="n">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A21" s="3">
         <v>2008</v>
       </c>
-      <c r="B21" s="4" t="n">
+      <c r="B21" s="4">
         <v>15.8</v>
       </c>
-      <c r="C21" s="4" t="n">
+      <c r="C21" s="4">
         <v>67.5</v>
       </c>
-      <c r="D21" s="4" t="n">
+      <c r="D21" s="4">
         <v>53.5</v>
       </c>
-      <c r="E21" s="4" t="n">
+      <c r="E21" s="4">
         <v>133.4</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="3" t="n">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A22" s="3">
         <v>2009</v>
       </c>
-      <c r="B22" s="4" t="n">
+      <c r="B22" s="4">
         <v>16</v>
       </c>
-      <c r="C22" s="4" t="n">
+      <c r="C22" s="4">
         <v>67.5</v>
       </c>
-      <c r="D22" s="4" t="n">
+      <c r="D22" s="4">
         <v>53.5</v>
       </c>
-      <c r="E22" s="4" t="n">
+      <c r="E22" s="4">
         <v>115.3</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="3" t="n">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A23" s="3">
         <v>2010</v>
       </c>
-      <c r="B23" s="4" t="n">
+      <c r="B23" s="4">
         <v>16.2</v>
       </c>
-      <c r="C23" s="4" t="n">
+      <c r="C23" s="4">
         <v>67</v>
       </c>
-      <c r="D23" s="4" t="n">
+      <c r="D23" s="4">
         <v>53.5</v>
       </c>
-      <c r="E23" s="4" t="n">
+      <c r="E23" s="4">
         <v>148.1</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="3" t="n">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A24" s="3">
         <v>2011</v>
       </c>
-      <c r="B24" s="4" t="n">
-        <v>16.4</v>
-      </c>
-      <c r="C24" s="4" t="n">
+      <c r="B24" s="4">
+        <v>16.399999999999999</v>
+      </c>
+      <c r="C24" s="4">
         <v>67</v>
       </c>
-      <c r="D24" s="4" t="n">
+      <c r="D24" s="4">
         <v>53.5</v>
       </c>
-      <c r="E24" s="4" t="n">
+      <c r="E24" s="4">
         <v>188</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="3" t="n">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A25" s="3">
         <v>2012</v>
       </c>
-      <c r="B25" s="4" t="n">
+      <c r="B25" s="4">
         <v>16.8</v>
       </c>
-      <c r="C25" s="4" t="n">
+      <c r="C25" s="4">
         <v>67.5</v>
       </c>
-      <c r="D25" s="4" t="n">
+      <c r="D25" s="4">
         <v>53.5</v>
       </c>
-      <c r="E25" s="4" t="n">
+      <c r="E25" s="4">
         <v>208</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="3" t="n">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A26" s="3">
         <v>2013</v>
       </c>
-      <c r="B26" s="4" t="n">
+      <c r="B26" s="4">
         <v>17</v>
       </c>
-      <c r="C26" s="4" t="n">
+      <c r="C26" s="4">
         <v>68</v>
       </c>
-      <c r="D26" s="4" t="n">
+      <c r="D26" s="4">
         <v>53.5</v>
       </c>
-      <c r="E26" s="4" t="n">
+      <c r="E26" s="4">
         <v>236.6</v>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="3" t="n">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A27" s="3">
         <v>2014</v>
       </c>
-      <c r="B27" s="4" t="n">
+      <c r="B27" s="4">
         <v>17.3</v>
       </c>
-      <c r="C27" s="4" t="n">
+      <c r="C27" s="4">
         <v>68</v>
       </c>
-      <c r="D27" s="4" t="n">
+      <c r="D27" s="4">
         <v>53.5</v>
       </c>
-      <c r="E27" s="4" t="n">
+      <c r="E27" s="4">
         <v>221.4</v>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="3" t="n">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A28" s="3">
         <v>2015</v>
       </c>
-      <c r="B28" s="4" t="n">
+      <c r="B28" s="4">
         <v>17.5</v>
       </c>
-      <c r="C28" s="4" t="n">
+      <c r="C28" s="4">
         <v>68</v>
       </c>
-      <c r="D28" s="4" t="n">
+      <c r="D28" s="4">
         <v>53.5</v>
       </c>
-      <c r="E28" s="4" t="n">
+      <c r="E28" s="4">
         <v>184.4</v>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="3" t="n">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A29" s="3">
         <v>2016</v>
       </c>
-      <c r="B29" s="4" t="n">
+      <c r="B29" s="4">
         <v>17.8</v>
       </c>
-      <c r="C29" s="4" t="n">
+      <c r="C29" s="4">
         <v>68</v>
       </c>
-      <c r="D29" s="4" t="n">
+      <c r="D29" s="4">
         <v>53.5</v>
       </c>
-      <c r="E29" s="4" t="n">
-        <v>137.3</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="3" t="n">
+      <c r="E29" s="4">
+        <v>137.30000000000001</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A30" s="3">
         <v>2017</v>
       </c>
-      <c r="B30" s="4" t="n">
+      <c r="B30" s="4">
         <v>18</v>
       </c>
-      <c r="C30" s="4" t="n">
+      <c r="C30" s="4">
         <v>67.5</v>
       </c>
-      <c r="D30" s="4" t="n">
+      <c r="D30" s="4">
         <v>57</v>
       </c>
-      <c r="E30" s="4" t="n">
+      <c r="E30" s="4">
         <v>166.8</v>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="3" t="n">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A31" s="3">
         <v>2018</v>
       </c>
-      <c r="B31" s="4" t="n">
+      <c r="B31" s="4">
         <v>18.2</v>
       </c>
-      <c r="C31" s="4" t="n">
+      <c r="C31" s="4">
         <v>67</v>
       </c>
-      <c r="D31" s="4" t="n">
+      <c r="D31" s="4">
         <v>57.2</v>
       </c>
-      <c r="E31" s="4" t="n">
+      <c r="E31" s="4">
         <v>179.3</v>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="3" t="n">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A32" s="3">
         <v>2019</v>
       </c>
-      <c r="B32" s="4" t="n">
+      <c r="B32" s="4">
         <v>18.5</v>
       </c>
-      <c r="C32" s="4" t="n">
+      <c r="C32" s="4">
         <v>67</v>
       </c>
-      <c r="D32" s="4" t="n">
+      <c r="D32" s="4">
         <v>57.5</v>
       </c>
-      <c r="E32" s="4" t="n">
+      <c r="E32" s="4">
         <v>181.7</v>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="3" t="n">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A33" s="3">
         <v>2020</v>
       </c>
-      <c r="B33" s="4" t="n">
+      <c r="B33" s="4">
         <v>18.8</v>
       </c>
-      <c r="C33" s="4" t="n">
+      <c r="C33" s="4">
         <v>67</v>
       </c>
-      <c r="D33" s="4" t="n">
+      <c r="D33" s="4">
         <v>57.5</v>
       </c>
-      <c r="E33" s="4" t="n">
+      <c r="E33" s="4">
         <v>171.1</v>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="3" t="n">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A34" s="3">
         <v>2021</v>
       </c>
-      <c r="B34" s="4" t="n">
+      <c r="B34" s="4">
         <v>19</v>
       </c>
-      <c r="C34" s="4" t="n">
+      <c r="C34" s="4">
         <v>66.8</v>
       </c>
-      <c r="D34" s="4" t="n">
+      <c r="D34" s="4">
         <v>57.7</v>
       </c>
-      <c r="E34" s="4" t="n">
+      <c r="E34" s="4">
         <v>197.1</v>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="3" t="n">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A35" s="3">
         <v>2022</v>
       </c>
-      <c r="B35" s="4" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="C35" s="4" t="n">
-        <v>66.59999999999999</v>
-      </c>
-      <c r="D35" s="4" t="n">
+      <c r="B35" s="4">
+        <v>19.600000000000001</v>
+      </c>
+      <c r="C35" s="4">
+        <v>66.599999999999994</v>
+      </c>
+      <c r="D35" s="4">
         <v>57.9</v>
       </c>
-      <c r="E35" s="4" t="n">
+      <c r="E35" s="4">
         <v>220.6</v>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="3" t="n">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A36" s="3">
         <v>2023</v>
       </c>
-      <c r="B36" s="4" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="C36" s="4" t="n">
+      <c r="B36" s="4">
+        <v>19.899999999999999</v>
+      </c>
+      <c r="C36" s="4">
         <v>66.5</v>
       </c>
-      <c r="D36" s="4" t="n">
+      <c r="D36" s="4">
         <v>58</v>
       </c>
-      <c r="E36" s="4" t="n">
-        <v>261.4</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="3" t="n">
+      <c r="E36" s="4">
+        <v>261.39999999999998</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A37" s="3">
         <v>2024</v>
       </c>
-      <c r="B37" s="4" t="n">
+      <c r="B37" s="4">
         <v>20.3</v>
       </c>
-      <c r="C37" s="4" t="n">
+      <c r="C37" s="4">
         <v>66.5</v>
       </c>
-      <c r="D37" s="4" t="n">
+      <c r="D37" s="4">
         <v>58.3</v>
       </c>
-      <c r="E37" s="4" t="n">
+      <c r="E37" s="4">
         <v>280</v>
       </c>
     </row>
@@ -1633,94 +1699,72 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:B8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col width="91" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
+    <col min="1" max="1" width="91" customWidth="1"/>
+    <col min="2" max="2" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t># Source: IRENA / countryeconomy.com. Base year 2023. Renewable share 12.4% of 113 TWh.</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>Share_pct</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>coal</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="n">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" s="4">
         <v>61</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>gas</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="n">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="4">
         <v>24</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>hydro</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="n">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A5" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" s="4">
         <v>8.5</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>wind</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="n">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A6" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" s="4">
         <v>3.5</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>solar</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="n">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A7" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7" s="4">
         <v>2</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>nuclear</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="n">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A8" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" s="4">
         <v>0</v>
       </c>
     </row>
@@ -1730,234 +1774,186 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:D13"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col width="61" customWidth="1" min="1" max="1"/>
-    <col width="35" customWidth="1" min="2" max="2"/>
-    <col width="44" customWidth="1" min="3" max="3"/>
-    <col width="45" customWidth="1" min="4" max="4"/>
+    <col min="1" max="1" width="61" customWidth="1"/>
+    <col min="2" max="2" width="35" customWidth="1"/>
+    <col min="3" max="3" width="44" customWidth="1"/>
+    <col min="4" max="4" width="45" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t># Scenario parameters. Adjust to your policy assumptions.</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Parameter</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>BAU</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>MT</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>DD</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="inlineStr">
-        <is>
-          <t>Business as Usual</t>
-        </is>
-      </c>
-      <c r="C3" s="5" t="inlineStr">
-        <is>
-          <t>Moderate Transition</t>
-        </is>
-      </c>
-      <c r="D3" s="5" t="inlineStr">
-        <is>
-          <t>Deep Decarbonization</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="inlineStr">
-        <is>
-          <t>Current policy, no new measures</t>
-        </is>
-      </c>
-      <c r="C4" s="5" t="inlineStr">
-        <is>
-          <t>NDC targets met, gradual coal phase-down</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="inlineStr">
-        <is>
-          <t>Carbon neutrality 2060, rapid RE scale-up</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>gdp_growth</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="n">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A2" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A3" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A4" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A5" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B5" s="4">
         <v>0.04</v>
       </c>
-      <c r="C5" s="4" t="n">
-        <v>0.042</v>
-      </c>
-      <c r="D5" s="4" t="n">
-        <v>0.043</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>energy_intensity_change</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="n">
+      <c r="C5" s="4">
+        <v>4.2000000000000003E-2</v>
+      </c>
+      <c r="D5" s="4">
+        <v>4.2999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A6" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B6" s="4">
         <v>-0.01</v>
       </c>
-      <c r="C6" s="4" t="n">
+      <c r="C6" s="4">
         <v>-0.02</v>
       </c>
-      <c r="D6" s="4" t="n">
+      <c r="D6" s="4">
         <v>-0.03</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>coal_share_2050</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="n">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A7" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B7" s="4">
         <v>0.45</v>
       </c>
-      <c r="C7" s="4" t="n">
+      <c r="C7" s="4">
         <v>0.25</v>
       </c>
-      <c r="D7" s="4" t="n">
+      <c r="D7" s="4">
         <v>0.05</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>renewables_2030</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="n">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A8" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B8" s="4">
         <v>0.08</v>
       </c>
-      <c r="C8" s="4" t="n">
+      <c r="C8" s="4">
         <v>0.15</v>
       </c>
-      <c r="D8" s="4" t="n">
+      <c r="D8" s="4">
         <v>0.22</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>renewables_2050</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="n">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A9" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B9" s="4">
         <v>0.15</v>
       </c>
-      <c r="C9" s="4" t="n">
+      <c r="C9" s="4">
         <v>0.4</v>
       </c>
-      <c r="D9" s="4" t="n">
+      <c r="D9" s="4">
         <v>0.7</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>nuclear_gw_2035</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="n">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A10" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B10" s="4">
         <v>0</v>
       </c>
-      <c r="C10" s="4" t="n">
+      <c r="C10" s="4">
         <v>1.2</v>
       </c>
-      <c r="D10" s="4" t="n">
+      <c r="D10" s="4">
         <v>2.4</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>co2_price_2030</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="n">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A11" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B11" s="5">
         <v>5</v>
       </c>
-      <c r="C11" s="5" t="n">
+      <c r="C11" s="5">
         <v>20</v>
       </c>
-      <c r="D11" s="5" t="n">
+      <c r="D11" s="5">
         <v>50</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>co2_price_2050</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="n">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A12" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B12" s="5">
         <v>10</v>
       </c>
-      <c r="C12" s="5" t="n">
+      <c r="C12" s="5">
         <v>50</v>
       </c>
-      <c r="D12" s="5" t="n">
+      <c r="D12" s="5">
         <v>150</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>ev_share_2050</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="n">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A13" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B13" s="4">
         <v>0.1</v>
       </c>
-      <c r="C13" s="4" t="n">
+      <c r="C13" s="4">
         <v>0.3</v>
       </c>
-      <c r="D13" s="4" t="n">
+      <c r="D13" s="4">
         <v>0.8</v>
       </c>
     </row>
@@ -1967,84 +1963,64 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:B7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col width="99" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
+    <col min="1" max="1" width="99" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t># Kazakhstan NDC (updated 2023): -15% unconditional, -25% conditional vs 1990. Neutrality 2060.</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Parameter</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>Value</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>base_year</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="n">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A2" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B3" s="5">
         <v>1990</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>base_co2_mt</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="n">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B4" s="4">
         <v>248.6</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>ndc_unconditional_pct</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="n">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A5" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B5" s="4">
         <v>-15</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>ndc_conditional_pct</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="n">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A6" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B6" s="4">
         <v>-25</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>neutrality_year</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="n">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A7" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B7" s="5">
         <v>2060</v>
       </c>
     </row>
